--- a/Test Data - 25.01.2026.xlsx
+++ b/Test Data - 25.01.2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Github\Data-Analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Sanjay_Github\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB8C6EB-F69F-464B-963E-DE926223EB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E6F31E-F95B-4EC6-AB62-6E8B40F7B616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{FC16F1F9-51EA-4971-8453-8D2010AD72C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{FC16F1F9-51EA-4971-8453-8D2010AD72C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Sheet11" sheetId="11" r:id="rId11"/>
     <sheet name="Sheet12" sheetId="12" r:id="rId12"/>
     <sheet name="Sheet13" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet1 (2)" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>Roll No</t>
   </si>
@@ -257,6 +258,30 @@
   </si>
   <si>
     <t>http://www.company.co.uk</t>
+  </si>
+  <si>
+    <t>+49 151-234-5678</t>
+  </si>
+  <si>
+    <t>+61 412-345-678</t>
+  </si>
+  <si>
+    <t>+91 98765-43210</t>
+  </si>
+  <si>
+    <t>+44 123-456-7890</t>
+  </si>
+  <si>
+    <t>+1 987-654-3210</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Clean Phone</t>
+  </si>
+  <si>
+    <t>Raw Phone</t>
   </si>
 </sst>
 </file>
@@ -292,8 +317,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1670,15 +1696,16 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{430F7097-3132-4340-8B3D-AA720B43A29A}">
-  <dimension ref="A4:C9"/>
+  <dimension ref="A4:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1689,41 +1716,277 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f>+FIND(".",A5)+1</f>
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <f>+LEN(A5)-FIND(".",A5)</f>
+        <v>10</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" ref="D5:D9" si="0">+MID(A5,B5,C5)</f>
+        <v>google.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" ref="B6:B9" si="1">+FIND(".",A6)+1</f>
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:C9" si="2">+LEN(A6)-FIND(".",A6)</f>
+        <v>9</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>amazon.in</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>example.org</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>wikipedia.org</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>company.co.uk</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" display="https://www.google.com/" xr:uid="{9421F184-6D8C-451A-A06C-738BCB7646F3}"/>
-    <hyperlink ref="A6" r:id="rId2" display="https://www.amazon.in/" xr:uid="{4EEA43CC-2BAB-443B-A2CF-7F190893871D}"/>
-    <hyperlink ref="A7" r:id="rId3" display="http://www.example.org/" xr:uid="{E8C4E400-BE63-4B24-B0C5-0BF137F7DEBA}"/>
-    <hyperlink ref="A8" r:id="rId4" display="https://www.wikipedia.org/" xr:uid="{1C8D4481-2944-4F69-8491-43954DE95EA6}"/>
-    <hyperlink ref="A9" r:id="rId5" display="http://www.company.co.uk/" xr:uid="{1093DEFB-66A1-4473-BB67-B0932A59DB7E}"/>
+    <hyperlink ref="A6" r:id="rId1" display="https://www.amazon.in/" xr:uid="{4EEA43CC-2BAB-443B-A2CF-7F190893871D}"/>
+    <hyperlink ref="A7" r:id="rId2" display="http://www.example.org/" xr:uid="{E8C4E400-BE63-4B24-B0C5-0BF137F7DEBA}"/>
+    <hyperlink ref="A8" r:id="rId3" display="https://www.wikipedia.org/" xr:uid="{1C8D4481-2944-4F69-8491-43954DE95EA6}"/>
+    <hyperlink ref="A9" r:id="rId4" display="http://www.company.co.uk/" xr:uid="{1093DEFB-66A1-4473-BB67-B0932A59DB7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373548BE-786B-460D-B44D-7807EB3299C8}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="str">
+        <f>+TRIM(SUBSTITUTE(A2,"-",""))</f>
+        <v>+1 9876543210</v>
+      </c>
+      <c r="C2" t="str">
+        <f>+LEFT(B2,FIND(" ",B2)-1)</f>
+        <v>+1</v>
+      </c>
+      <c r="D2">
+        <f>+FIND(" ",B2)</f>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <f>+LEN(B2)-FIND(" ",B2)</f>
+        <v>10</v>
+      </c>
+      <c r="F2" t="str">
+        <f>+MID(B2,D2,E2)</f>
+        <v xml:space="preserve"> 987654321</v>
+      </c>
+      <c r="G2" t="str">
+        <f>+MID(B2,FIND(" ",B2),LEN(B2)-FIND(" ",B2))</f>
+        <v xml:space="preserve"> 987654321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="str">
+        <f>+TRIM(SUBSTITUTE(A3,"-",""))</f>
+        <v>+44 1234567890</v>
+      </c>
+      <c r="C3" t="str">
+        <f>+LEFT(B3,FIND(" ",B3)-1)</f>
+        <v>+44</v>
+      </c>
+      <c r="D3">
+        <f>+FIND(" ",B3)</f>
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>+LEN(B3)-FIND(" ",B3)</f>
+        <v>10</v>
+      </c>
+      <c r="F3" t="str">
+        <f>+MID(B3,D3,E3)</f>
+        <v xml:space="preserve"> 123456789</v>
+      </c>
+      <c r="G3" t="str">
+        <f>+MID(B3,FIND(" ",B3),LEN(B3)-FIND(" ",B3))</f>
+        <v xml:space="preserve"> 123456789</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="str">
+        <f>+TRIM(SUBSTITUTE(A4,"-",""))</f>
+        <v>+91 9876543210</v>
+      </c>
+      <c r="C4" t="str">
+        <f>+LEFT(B4,FIND(" ",B4)-1)</f>
+        <v>+91</v>
+      </c>
+      <c r="D4">
+        <f>+FIND(" ",B4)</f>
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <f>+LEN(B4)-FIND(" ",B4)</f>
+        <v>10</v>
+      </c>
+      <c r="F4" t="str">
+        <f>+MID(B4,D4,E4)</f>
+        <v xml:space="preserve"> 987654321</v>
+      </c>
+      <c r="G4" t="str">
+        <f>+MID(B4,FIND(" ",B4),LEN(B4)-FIND(" ",B4))</f>
+        <v xml:space="preserve"> 987654321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="str">
+        <f>+TRIM(SUBSTITUTE(A5,"-",""))</f>
+        <v>+61 412345678</v>
+      </c>
+      <c r="C5" t="str">
+        <f>+LEFT(B5,FIND(" ",B5)-1)</f>
+        <v>+61</v>
+      </c>
+      <c r="D5">
+        <f>+FIND(" ",B5)</f>
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <f>+LEN(B5)-FIND(" ",B5)</f>
+        <v>9</v>
+      </c>
+      <c r="F5" t="str">
+        <f>+MID(B5,D5,E5)</f>
+        <v xml:space="preserve"> 41234567</v>
+      </c>
+      <c r="G5" t="str">
+        <f>+MID(B5,FIND(" ",B5),LEN(B5)-FIND(" ",B5))</f>
+        <v xml:space="preserve"> 41234567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="str">
+        <f>+TRIM(SUBSTITUTE(A6,"-",""))</f>
+        <v>+49 1512345678</v>
+      </c>
+      <c r="C6" t="str">
+        <f>+LEFT(B6,FIND(" ",B6)-1)</f>
+        <v>+49</v>
+      </c>
+      <c r="D6">
+        <f>+FIND(" ",B6)</f>
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <f>+LEN(B6)-FIND(" ",B6)</f>
+        <v>10</v>
+      </c>
+      <c r="F6" t="str">
+        <f>+MID(B6,D6,E6)</f>
+        <v xml:space="preserve"> 151234567</v>
+      </c>
+      <c r="G6" t="str">
+        <f>+MID(B6,FIND(" ",B6),LEN(B6)-FIND(" ",B6))</f>
+        <v xml:space="preserve"> 151234567</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
